--- a/OBIBv2.1/Sample,SmpleDonor,Event_ONTOLOGIZATION.xlsx
+++ b/OBIBv2.1/Sample,SmpleDonor,Event_ONTOLOGIZATION.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="sample,sample donor,event" sheetId="1" r:id="rId1"/>
@@ -382,9 +382,6 @@
   </si>
   <si>
     <t>http://purl.obolibrary.org/obo/IAO_0000030</t>
-  </si>
-  <si>
-    <t>dataset type</t>
   </si>
   <si>
     <t>Birth date</t>
@@ -983,6 +980,9 @@
   </si>
   <si>
     <t>donates</t>
+  </si>
+  <si>
+    <t>sample donor dataset type</t>
   </si>
 </sst>
 </file>
@@ -1598,10 +1598,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>7</v>
@@ -1610,7 +1610,7 @@
         <v>8</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>10</v>
@@ -1650,17 +1650,17 @@
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N2" s="14"/>
       <c r="P2" s="15"/>
@@ -1700,7 +1700,7 @@
         <v>19</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>20</v>
@@ -1709,16 +1709,16 @@
         <v>21</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>22</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P3" s="15"/>
       <c r="Q3" s="3"/>
@@ -1757,7 +1757,7 @@
         <v>26</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="19" t="s">
@@ -1767,16 +1767,16 @@
         <v>28</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P4" s="18"/>
       <c r="Q4" s="19"/>
@@ -1815,7 +1815,7 @@
         <v>33</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>34</v>
@@ -1824,16 +1824,16 @@
         <v>35</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P5" s="20"/>
       <c r="Q5" s="3"/>
@@ -1869,7 +1869,7 @@
         <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>40</v>
@@ -1881,16 +1881,16 @@
         <v>42</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L6" s="13" t="s">
         <v>43</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N6" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P6" s="18"/>
       <c r="Q6" s="3"/>
@@ -1930,7 +1930,7 @@
         <v>48</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>49</v>
@@ -1942,10 +1942,10 @@
         <v>51</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M7" s="13" t="s">
         <v>52</v>
@@ -1989,7 +1989,7 @@
         <v>56</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>57</v>
@@ -2001,10 +2001,10 @@
         <v>55</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M8" s="13" t="s">
         <v>58</v>
@@ -2048,7 +2048,7 @@
         <v>56</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>63</v>
@@ -2060,10 +2060,10 @@
         <v>62</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M9" s="13" t="s">
         <v>58</v>
@@ -2107,7 +2107,7 @@
         <v>68</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>69</v>
@@ -2119,13 +2119,13 @@
         <v>67</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N10" s="3"/>
       <c r="P10" s="3"/>
@@ -2166,7 +2166,7 @@
         <v>56</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>74</v>
@@ -2178,13 +2178,13 @@
         <v>73</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N11" s="3"/>
       <c r="P11" s="3"/>
@@ -2225,7 +2225,7 @@
         <v>56</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="19" t="s">
@@ -2235,7 +2235,7 @@
         <v>78</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N12" s="3"/>
       <c r="P12" s="19"/>
@@ -2276,7 +2276,7 @@
         <v>82</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>83</v>
@@ -2288,16 +2288,16 @@
         <v>81</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>84</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
@@ -2337,7 +2337,7 @@
         <v>88</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>89</v>
@@ -2349,16 +2349,16 @@
         <v>91</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -2404,10 +2404,10 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N15" s="3"/>
       <c r="P15" s="3"/>
@@ -2462,7 +2462,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="5"/>
@@ -2472,7 +2472,7 @@
         <v>98</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>99</v>
@@ -2481,10 +2481,10 @@
         <v>100</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N17" s="3"/>
       <c r="P17" s="3"/>
@@ -2522,10 +2522,10 @@
         <v>103</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>104</v>
@@ -2537,7 +2537,7 @@
         <v>103</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>106</v>
@@ -2584,7 +2584,7 @@
         <v>111</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>112</v>
@@ -2593,16 +2593,16 @@
         <v>113</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -2642,26 +2642,26 @@
         <v>117</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="19" t="s">
-        <v>119</v>
+        <v>222</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>116</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P20" s="19"/>
       <c r="Q20" s="19"/>
@@ -2692,37 +2692,37 @@
         <v>114</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="F21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="H21" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="K21" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="N21" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
@@ -2730,7 +2730,7 @@
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
       <c r="U21" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2781,19 +2781,19 @@
       <c r="F23" s="5"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="K23" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N23" s="3"/>
       <c r="P23" s="3"/>
@@ -2816,35 +2816,35 @@
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" s="22" t="s">
+      <c r="E24" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="22" t="s">
-        <v>133</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="K24" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>106</v>
@@ -2870,41 +2870,41 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="22" t="s">
+      <c r="E25" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="22" t="s">
-        <v>139</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G25" s="13"/>
       <c r="H25" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="N25" s="3"/>
       <c r="P25" s="3"/>
@@ -2927,41 +2927,41 @@
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="22" t="s">
-        <v>146</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G26" s="13"/>
       <c r="H26" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="K26" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="M26" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="N26" s="3"/>
       <c r="P26" s="3"/>
@@ -2984,44 +2984,44 @@
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D27" s="22" t="s">
+      <c r="E27" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="E27" s="22" t="s">
-        <v>153</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="M27" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I27" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="N27" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
@@ -3154,22 +3154,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -3180,10 +3180,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -3200,10 +3200,10 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>34</v>
@@ -3220,10 +3220,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>41</v>
@@ -3240,10 +3240,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>50</v>
@@ -3260,10 +3260,10 @@
         <v>49</v>
       </c>
       <c r="C6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>220</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>54</v>
@@ -3280,10 +3280,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>220</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>61</v>
@@ -3300,10 +3300,10 @@
         <v>69</v>
       </c>
       <c r="C8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>220</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>66</v>
@@ -3320,10 +3320,10 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>220</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>72</v>
@@ -3340,10 +3340,10 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>80</v>
@@ -3360,10 +3360,10 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>90</v>
@@ -3380,10 +3380,10 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>207</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>96</v>
@@ -3405,7 +3405,7 @@
         <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>69</v>
@@ -3414,7 +3414,7 @@
         <v>105</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -3425,13 +3425,13 @@
         <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>111</v>
@@ -3445,16 +3445,16 @@
         <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -3465,19 +3465,19 @@
         <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D17" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E17" t="s">
+        <v>182</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="E17" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -3488,10 +3488,10 @@
         <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -3507,82 +3507,82 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
